--- a/data/saeop/상담사업.xlsx
+++ b/data/saeop/상담사업.xlsx
@@ -560,7 +560,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J44"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -1768,9 +1768,137 @@
         <v/>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>O</v>
+      </c>
+      <c r="B41" t="str">
+        <v>sangdam</v>
+      </c>
+      <c r="C41" t="str">
+        <v/>
+      </c>
+      <c r="D41" t="str">
+        <v>집단 프로그램</v>
+      </c>
+      <c r="E41" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F41" t="str">
+        <v>집단상담</v>
+      </c>
+      <c r="G41" t="str">
+        <v>집단_상담_3.jpg</v>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+      <c r="J41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>O</v>
+      </c>
+      <c r="B42" t="str">
+        <v>sangdam</v>
+      </c>
+      <c r="C42" t="str">
+        <v/>
+      </c>
+      <c r="D42" t="str">
+        <v>집단 프로그램</v>
+      </c>
+      <c r="E42" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F42" t="str">
+        <v>집단상담</v>
+      </c>
+      <c r="G42" t="str">
+        <v>집단상담_1.jpg</v>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>O</v>
+      </c>
+      <c r="B43" t="str">
+        <v>sangdam</v>
+      </c>
+      <c r="C43" t="str">
+        <v/>
+      </c>
+      <c r="D43" t="str">
+        <v>집단 프로그램</v>
+      </c>
+      <c r="E43" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F43" t="str">
+        <v>집단상담</v>
+      </c>
+      <c r="G43" t="str">
+        <v>집단상담_4.jpg</v>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>O</v>
+      </c>
+      <c r="B44" t="str">
+        <v>sangdam</v>
+      </c>
+      <c r="C44" t="str">
+        <v/>
+      </c>
+      <c r="D44" t="str">
+        <v>집단 프로그램</v>
+      </c>
+      <c r="E44" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F44" t="str">
+        <v>집단상담</v>
+      </c>
+      <c r="G44" t="str">
+        <v>집단상담.jpg</v>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J40"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J44"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/saeop/상담사업.xlsx
+++ b/data/saeop/상담사업.xlsx
@@ -560,7 +560,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J43"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -985,10 +985,10 @@
         <v>사진</v>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>신입회원교육</v>
       </c>
       <c r="G16" t="str">
-        <v>신입회원교육_(2).jpg</v>
+        <v>신입회원교육_(1).jpg</v>
       </c>
       <c r="H16" t="str">
         <v/>
@@ -1017,10 +1017,10 @@
         <v>사진</v>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>신입회원교육</v>
       </c>
       <c r="G17" t="str">
-        <v>집단상담_1.jpg</v>
+        <v>신입회원교육_(2).jpg</v>
       </c>
       <c r="H17" t="str">
         <v/>
@@ -1049,10 +1049,10 @@
         <v>사진</v>
       </c>
       <c r="F18" t="str">
-        <v/>
+        <v>신입회원교육</v>
       </c>
       <c r="G18" t="str">
-        <v>집단상담.jpg</v>
+        <v>신입회원교육_(3).jpg</v>
       </c>
       <c r="H18" t="str">
         <v/>
@@ -1075,16 +1075,16 @@
         <v/>
       </c>
       <c r="D19" t="str">
-        <v>일반상담</v>
+        <v>전문상담</v>
       </c>
       <c r="E19" t="str">
-        <v>사진</v>
+        <v>설명</v>
       </c>
       <c r="F19" t="str">
         <v/>
       </c>
       <c r="G19" t="str">
-        <v>집단상담_2.jpg</v>
+        <v>복지관 이용 회원의 다양한 고민과 어려움 해결을 위한 전문가 상담을 연계하여, 적절한 정보를 제공함으로써 행복한 삶을 살아갈 수 있도록 지원합니다.</v>
       </c>
       <c r="H19" t="str">
         <v/>
@@ -1110,16 +1110,16 @@
         <v>전문상담</v>
       </c>
       <c r="E20" t="str">
-        <v>설명</v>
+        <v>정보</v>
       </c>
       <c r="F20" t="str">
-        <v/>
+        <v>이용 대상</v>
       </c>
       <c r="G20" t="str">
-        <v>복지관 이용 회원의 다양한 고민과 어려움 해결을 위한 전문가 상담을 연계하여, 적절한 정보를 제공함으로써 행복한 삶을 살아갈 수 있도록 지원합니다.</v>
+        <v>복지관 이용 회원</v>
       </c>
       <c r="H20" t="str">
-        <v/>
+        <v>user</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1145,13 +1145,13 @@
         <v>정보</v>
       </c>
       <c r="F21" t="str">
-        <v>이용 대상</v>
+        <v>이용 시간</v>
       </c>
       <c r="G21" t="str">
-        <v>복지관 이용 회원</v>
+        <v>전문 상담 진행 시 개별 안내</v>
       </c>
       <c r="H21" t="str">
-        <v>user</v>
+        <v>clock</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -1177,16 +1177,16 @@
         <v>정보</v>
       </c>
       <c r="F22" t="str">
-        <v>이용 시간</v>
+        <v>문의</v>
       </c>
       <c r="G22" t="str">
-        <v>전문 상담 진행 시 개별 안내</v>
+        <v>문화사업팀 033-747-0516</v>
       </c>
       <c r="H22" t="str">
-        <v>clock</v>
+        <v>phone</v>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>033-747-0516</v>
       </c>
       <c r="J22" t="str">
         <v/>
@@ -1206,19 +1206,19 @@
         <v>전문상담</v>
       </c>
       <c r="E23" t="str">
-        <v>정보</v>
+        <v>절차제목</v>
       </c>
       <c r="F23" t="str">
-        <v>문의</v>
+        <v/>
       </c>
       <c r="G23" t="str">
-        <v>문화사업팀 033-747-0516</v>
+        <v>이용 절차</v>
       </c>
       <c r="H23" t="str">
-        <v>phone</v>
+        <v/>
       </c>
       <c r="I23" t="str">
-        <v>033-747-0516</v>
+        <v/>
       </c>
       <c r="J23" t="str">
         <v/>
@@ -1238,13 +1238,13 @@
         <v>전문상담</v>
       </c>
       <c r="E24" t="str">
-        <v>절차제목</v>
+        <v>절차</v>
       </c>
       <c r="F24" t="str">
-        <v/>
+        <v>사전 접수·상담</v>
       </c>
       <c r="G24" t="str">
-        <v>이용 절차</v>
+        <v>신청 기간 안에 사전 접수와 상담을 진행합니다.</v>
       </c>
       <c r="H24" t="str">
         <v/>
@@ -1273,10 +1273,10 @@
         <v>절차</v>
       </c>
       <c r="F25" t="str">
-        <v>사전 접수·상담</v>
+        <v>전문가 상담 일정 안내</v>
       </c>
       <c r="G25" t="str">
-        <v>신청 기간 안에 사전 접수와 상담을 진행합니다.</v>
+        <v>상담 일정을 개별적으로 안내해 드립니다.</v>
       </c>
       <c r="H25" t="str">
         <v/>
@@ -1305,10 +1305,10 @@
         <v>절차</v>
       </c>
       <c r="F26" t="str">
-        <v>전문가 상담 일정 안내</v>
+        <v>전문가 상담 진행</v>
       </c>
       <c r="G26" t="str">
-        <v>상담 일정을 개별적으로 안내해 드립니다.</v>
+        <v>전문가와 상담을 진행합니다.</v>
       </c>
       <c r="H26" t="str">
         <v/>
@@ -1334,13 +1334,13 @@
         <v>전문상담</v>
       </c>
       <c r="E27" t="str">
-        <v>절차</v>
+        <v>내용제목</v>
       </c>
       <c r="F27" t="str">
-        <v>전문가 상담 진행</v>
+        <v/>
       </c>
       <c r="G27" t="str">
-        <v>전문가와 상담을 진행합니다.</v>
+        <v>이런 상담을 해드려요</v>
       </c>
       <c r="H27" t="str">
         <v/>
@@ -1366,13 +1366,13 @@
         <v>전문상담</v>
       </c>
       <c r="E28" t="str">
-        <v>내용제목</v>
+        <v>내용</v>
       </c>
       <c r="F28" t="str">
-        <v/>
+        <v>스트레스 상담</v>
       </c>
       <c r="G28" t="str">
-        <v>이런 상담을 해드려요</v>
+        <v>우울 및 스트레스 등 정신건강 관련 상담</v>
       </c>
       <c r="H28" t="str">
         <v/>
@@ -1401,10 +1401,10 @@
         <v>내용</v>
       </c>
       <c r="F29" t="str">
-        <v>스트레스 상담</v>
+        <v>전문 심리상담</v>
       </c>
       <c r="G29" t="str">
-        <v>우울 및 스트레스 등 정신건강 관련 상담</v>
+        <v>개인 심리상담</v>
       </c>
       <c r="H29" t="str">
         <v/>
@@ -1436,7 +1436,7 @@
         <v>전문 심리상담</v>
       </c>
       <c r="G30" t="str">
-        <v>개인 심리상담</v>
+        <v>부부 갈등 완화를 위한 상담 등</v>
       </c>
       <c r="H30" t="str">
         <v/>
@@ -1459,16 +1459,16 @@
         <v/>
       </c>
       <c r="D31" t="str">
-        <v>전문상담</v>
+        <v>집단 프로그램</v>
       </c>
       <c r="E31" t="str">
-        <v>내용</v>
+        <v>부제</v>
       </c>
       <c r="F31" t="str">
-        <v>전문 심리상담</v>
+        <v/>
       </c>
       <c r="G31" t="str">
-        <v>부부 갈등 완화를 위한 상담 등</v>
+        <v>노년기 우울예방 프로그램</v>
       </c>
       <c r="H31" t="str">
         <v/>
@@ -1494,13 +1494,13 @@
         <v>집단 프로그램</v>
       </c>
       <c r="E32" t="str">
-        <v>부제</v>
+        <v>설명</v>
       </c>
       <c r="F32" t="str">
         <v/>
       </c>
       <c r="G32" t="str">
-        <v>노년기 우울예방 프로그램</v>
+        <v>비슷한 어려움을 가진 어르신들이 함께 참여하는 집단 활동으로, 우울을 예방하고 서로 어울리며 건강한 노년을 보내실 수 있도록 지원합니다.</v>
       </c>
       <c r="H32" t="str">
         <v/>
@@ -1526,16 +1526,16 @@
         <v>집단 프로그램</v>
       </c>
       <c r="E33" t="str">
-        <v>설명</v>
+        <v>정보</v>
       </c>
       <c r="F33" t="str">
-        <v/>
+        <v>이용 대상</v>
       </c>
       <c r="G33" t="str">
-        <v>비슷한 어려움을 가진 어르신들이 함께 참여하는 집단 활동으로, 우울을 예방하고 서로 어울리며 건강한 노년을 보내실 수 있도록 지원합니다.</v>
+        <v>우울 예방 프로그램 참여를 희망하는 복지관 이용 회원</v>
       </c>
       <c r="H33" t="str">
-        <v/>
+        <v>user</v>
       </c>
       <c r="I33" t="str">
         <v/>
@@ -1561,13 +1561,13 @@
         <v>정보</v>
       </c>
       <c r="F34" t="str">
-        <v>이용 대상</v>
+        <v>운영 시간</v>
       </c>
       <c r="G34" t="str">
-        <v>우울 예방 프로그램 참여를 희망하는 복지관 이용 회원</v>
+        <v>7월 · 매주 목요일 10:00 – 11:30</v>
       </c>
       <c r="H34" t="str">
-        <v>user</v>
+        <v>clock</v>
       </c>
       <c r="I34" t="str">
         <v/>
@@ -1593,13 +1593,13 @@
         <v>정보</v>
       </c>
       <c r="F35" t="str">
-        <v>운영 시간</v>
+        <v>신청 방법</v>
       </c>
       <c r="G35" t="str">
-        <v>7월 · 매주 목요일 10:00 – 11:30</v>
+        <v>신청 기간 내 사전 신청</v>
       </c>
       <c r="H35" t="str">
-        <v>clock</v>
+        <v>edit</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -1625,16 +1625,16 @@
         <v>정보</v>
       </c>
       <c r="F36" t="str">
-        <v>신청 방법</v>
+        <v>문의</v>
       </c>
       <c r="G36" t="str">
-        <v>신청 기간 내 사전 신청</v>
+        <v>문화사업팀 033-747-0516</v>
       </c>
       <c r="H36" t="str">
-        <v>edit</v>
+        <v>phone</v>
       </c>
       <c r="I36" t="str">
-        <v/>
+        <v>033-747-0516</v>
       </c>
       <c r="J36" t="str">
         <v/>
@@ -1654,19 +1654,19 @@
         <v>집단 프로그램</v>
       </c>
       <c r="E37" t="str">
-        <v>정보</v>
+        <v>내용제목</v>
       </c>
       <c r="F37" t="str">
-        <v>문의</v>
+        <v/>
       </c>
       <c r="G37" t="str">
-        <v>문화사업팀 033-747-0516</v>
+        <v>이런 활동을 해요</v>
       </c>
       <c r="H37" t="str">
-        <v>phone</v>
+        <v/>
       </c>
       <c r="I37" t="str">
-        <v>033-747-0516</v>
+        <v/>
       </c>
       <c r="J37" t="str">
         <v/>
@@ -1686,13 +1686,13 @@
         <v>집단 프로그램</v>
       </c>
       <c r="E38" t="str">
-        <v>내용제목</v>
+        <v>내용</v>
       </c>
       <c r="F38" t="str">
-        <v/>
+        <v>우울 예방 교육</v>
       </c>
       <c r="G38" t="str">
-        <v>이런 활동을 해요</v>
+        <v>노년기 우울 예방을 위한 교육</v>
       </c>
       <c r="H38" t="str">
         <v/>
@@ -1721,10 +1721,10 @@
         <v>내용</v>
       </c>
       <c r="F39" t="str">
-        <v>우울 예방 교육</v>
+        <v>만들기 활동</v>
       </c>
       <c r="G39" t="str">
-        <v>노년기 우울 예방을 위한 교육</v>
+        <v>캘리그라피 무드등, 키링 등 손으로 만드는 활동</v>
       </c>
       <c r="H39" t="str">
         <v/>
@@ -1750,13 +1750,13 @@
         <v>집단 프로그램</v>
       </c>
       <c r="E40" t="str">
-        <v>내용</v>
+        <v>사진</v>
       </c>
       <c r="F40" t="str">
-        <v>만들기 활동</v>
+        <v>집단상담</v>
       </c>
       <c r="G40" t="str">
-        <v>캘리그라피 무드등, 키링 등 손으로 만드는 활동</v>
+        <v>집단_상담_3.jpg</v>
       </c>
       <c r="H40" t="str">
         <v/>
@@ -1788,7 +1788,7 @@
         <v>집단상담</v>
       </c>
       <c r="G41" t="str">
-        <v>집단_상담_3.jpg</v>
+        <v>집단상담_1.jpg</v>
       </c>
       <c r="H41" t="str">
         <v/>
@@ -1820,7 +1820,7 @@
         <v>집단상담</v>
       </c>
       <c r="G42" t="str">
-        <v>집단상담_1.jpg</v>
+        <v>집단상담_4.jpg</v>
       </c>
       <c r="H42" t="str">
         <v/>
@@ -1852,7 +1852,7 @@
         <v>집단상담</v>
       </c>
       <c r="G43" t="str">
-        <v>집단상담_4.jpg</v>
+        <v>집단상담.jpg</v>
       </c>
       <c r="H43" t="str">
         <v/>
@@ -1861,44 +1861,12 @@
         <v/>
       </c>
       <c r="J43" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>O</v>
-      </c>
-      <c r="B44" t="str">
-        <v>sangdam</v>
-      </c>
-      <c r="C44" t="str">
-        <v/>
-      </c>
-      <c r="D44" t="str">
-        <v>집단 프로그램</v>
-      </c>
-      <c r="E44" t="str">
-        <v>사진</v>
-      </c>
-      <c r="F44" t="str">
-        <v>집단상담</v>
-      </c>
-      <c r="G44" t="str">
-        <v>집단상담.jpg</v>
-      </c>
-      <c r="H44" t="str">
-        <v/>
-      </c>
-      <c r="I44" t="str">
-        <v/>
-      </c>
-      <c r="J44" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J44"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J43"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/saeop/상담사업.xlsx
+++ b/data/saeop/상담사업.xlsx
@@ -560,7 +560,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J47"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -1459,16 +1459,16 @@
         <v/>
       </c>
       <c r="D31" t="str">
-        <v>집단 프로그램</v>
+        <v>전문상담</v>
       </c>
       <c r="E31" t="str">
-        <v>부제</v>
+        <v>사진</v>
       </c>
       <c r="F31" t="str">
-        <v/>
+        <v>전문상담</v>
       </c>
       <c r="G31" t="str">
-        <v>노년기 우울예방 프로그램</v>
+        <v>일반상담.jpg</v>
       </c>
       <c r="H31" t="str">
         <v/>
@@ -1491,16 +1491,16 @@
         <v/>
       </c>
       <c r="D32" t="str">
-        <v>집단 프로그램</v>
+        <v>전문상담</v>
       </c>
       <c r="E32" t="str">
-        <v>설명</v>
+        <v>사진</v>
       </c>
       <c r="F32" t="str">
-        <v/>
+        <v>전문상담</v>
       </c>
       <c r="G32" t="str">
-        <v>비슷한 어려움을 가진 어르신들이 함께 참여하는 집단 활동으로, 우울을 예방하고 서로 어울리며 건강한 노년을 보내실 수 있도록 지원합니다.</v>
+        <v>전문상담_(2).jpg</v>
       </c>
       <c r="H32" t="str">
         <v/>
@@ -1523,19 +1523,19 @@
         <v/>
       </c>
       <c r="D33" t="str">
-        <v>집단 프로그램</v>
+        <v>전문상담</v>
       </c>
       <c r="E33" t="str">
-        <v>정보</v>
+        <v>사진</v>
       </c>
       <c r="F33" t="str">
-        <v>이용 대상</v>
+        <v>전문상담</v>
       </c>
       <c r="G33" t="str">
-        <v>우울 예방 프로그램 참여를 희망하는 복지관 이용 회원</v>
+        <v>전문상담_(3).jpg</v>
       </c>
       <c r="H33" t="str">
-        <v>user</v>
+        <v/>
       </c>
       <c r="I33" t="str">
         <v/>
@@ -1555,19 +1555,19 @@
         <v/>
       </c>
       <c r="D34" t="str">
-        <v>집단 프로그램</v>
+        <v>전문상담</v>
       </c>
       <c r="E34" t="str">
-        <v>정보</v>
+        <v>사진</v>
       </c>
       <c r="F34" t="str">
-        <v>운영 시간</v>
+        <v>전문상담</v>
       </c>
       <c r="G34" t="str">
-        <v>7월 · 매주 목요일 10:00 – 11:30</v>
+        <v>전문상담_(4).jpg</v>
       </c>
       <c r="H34" t="str">
-        <v>clock</v>
+        <v/>
       </c>
       <c r="I34" t="str">
         <v/>
@@ -1590,16 +1590,16 @@
         <v>집단 프로그램</v>
       </c>
       <c r="E35" t="str">
-        <v>정보</v>
+        <v>부제</v>
       </c>
       <c r="F35" t="str">
-        <v>신청 방법</v>
+        <v/>
       </c>
       <c r="G35" t="str">
-        <v>신청 기간 내 사전 신청</v>
+        <v>노년기 우울예방 프로그램</v>
       </c>
       <c r="H35" t="str">
-        <v>edit</v>
+        <v/>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -1622,19 +1622,19 @@
         <v>집단 프로그램</v>
       </c>
       <c r="E36" t="str">
-        <v>정보</v>
+        <v>설명</v>
       </c>
       <c r="F36" t="str">
-        <v>문의</v>
+        <v/>
       </c>
       <c r="G36" t="str">
-        <v>문화사업팀 033-747-0516</v>
+        <v>비슷한 어려움을 가진 어르신들이 함께 참여하는 집단 활동으로, 우울을 예방하고 서로 어울리며 건강한 노년을 보내실 수 있도록 지원합니다.</v>
       </c>
       <c r="H36" t="str">
-        <v>phone</v>
+        <v/>
       </c>
       <c r="I36" t="str">
-        <v>033-747-0516</v>
+        <v/>
       </c>
       <c r="J36" t="str">
         <v/>
@@ -1654,16 +1654,16 @@
         <v>집단 프로그램</v>
       </c>
       <c r="E37" t="str">
-        <v>내용제목</v>
+        <v>정보</v>
       </c>
       <c r="F37" t="str">
-        <v/>
+        <v>이용 대상</v>
       </c>
       <c r="G37" t="str">
-        <v>이런 활동을 해요</v>
+        <v>우울 예방 프로그램 참여를 희망하는 복지관 이용 회원</v>
       </c>
       <c r="H37" t="str">
-        <v/>
+        <v>user</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -1686,16 +1686,16 @@
         <v>집단 프로그램</v>
       </c>
       <c r="E38" t="str">
-        <v>내용</v>
+        <v>정보</v>
       </c>
       <c r="F38" t="str">
-        <v>우울 예방 교육</v>
+        <v>운영 시간</v>
       </c>
       <c r="G38" t="str">
-        <v>노년기 우울 예방을 위한 교육</v>
+        <v>7월 · 매주 목요일 10:00 – 11:30</v>
       </c>
       <c r="H38" t="str">
-        <v/>
+        <v>clock</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -1718,16 +1718,16 @@
         <v>집단 프로그램</v>
       </c>
       <c r="E39" t="str">
-        <v>내용</v>
+        <v>정보</v>
       </c>
       <c r="F39" t="str">
-        <v>만들기 활동</v>
+        <v>신청 방법</v>
       </c>
       <c r="G39" t="str">
-        <v>캘리그라피 무드등, 키링 등 손으로 만드는 활동</v>
+        <v>신청 기간 내 사전 신청</v>
       </c>
       <c r="H39" t="str">
-        <v/>
+        <v>edit</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -1750,19 +1750,19 @@
         <v>집단 프로그램</v>
       </c>
       <c r="E40" t="str">
-        <v>사진</v>
+        <v>정보</v>
       </c>
       <c r="F40" t="str">
-        <v>집단상담</v>
+        <v>문의</v>
       </c>
       <c r="G40" t="str">
-        <v>집단_상담_3.jpg</v>
+        <v>문화사업팀 033-747-0516</v>
       </c>
       <c r="H40" t="str">
-        <v/>
+        <v>phone</v>
       </c>
       <c r="I40" t="str">
-        <v/>
+        <v>033-747-0516</v>
       </c>
       <c r="J40" t="str">
         <v/>
@@ -1782,13 +1782,13 @@
         <v>집단 프로그램</v>
       </c>
       <c r="E41" t="str">
-        <v>사진</v>
+        <v>내용제목</v>
       </c>
       <c r="F41" t="str">
-        <v>집단상담</v>
+        <v/>
       </c>
       <c r="G41" t="str">
-        <v>집단상담_1.jpg</v>
+        <v>이런 활동을 해요</v>
       </c>
       <c r="H41" t="str">
         <v/>
@@ -1814,13 +1814,13 @@
         <v>집단 프로그램</v>
       </c>
       <c r="E42" t="str">
-        <v>사진</v>
+        <v>내용</v>
       </c>
       <c r="F42" t="str">
-        <v>집단상담</v>
+        <v>우울 예방 교육</v>
       </c>
       <c r="G42" t="str">
-        <v>집단상담_4.jpg</v>
+        <v>노년기 우울 예방을 위한 교육</v>
       </c>
       <c r="H42" t="str">
         <v/>
@@ -1846,27 +1846,155 @@
         <v>집단 프로그램</v>
       </c>
       <c r="E43" t="str">
+        <v>내용</v>
+      </c>
+      <c r="F43" t="str">
+        <v>만들기 활동</v>
+      </c>
+      <c r="G43" t="str">
+        <v>캘리그라피 무드등, 키링 등 손으로 만드는 활동</v>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>O</v>
+      </c>
+      <c r="B44" t="str">
+        <v>sangdam</v>
+      </c>
+      <c r="C44" t="str">
+        <v/>
+      </c>
+      <c r="D44" t="str">
+        <v>집단 프로그램</v>
+      </c>
+      <c r="E44" t="str">
         <v>사진</v>
       </c>
-      <c r="F43" t="str">
+      <c r="F44" t="str">
         <v>집단상담</v>
       </c>
-      <c r="G43" t="str">
+      <c r="G44" t="str">
+        <v>집단_상담_3.jpg</v>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>O</v>
+      </c>
+      <c r="B45" t="str">
+        <v>sangdam</v>
+      </c>
+      <c r="C45" t="str">
+        <v/>
+      </c>
+      <c r="D45" t="str">
+        <v>집단 프로그램</v>
+      </c>
+      <c r="E45" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F45" t="str">
+        <v>집단상담</v>
+      </c>
+      <c r="G45" t="str">
+        <v>집단상담_1.jpg</v>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>O</v>
+      </c>
+      <c r="B46" t="str">
+        <v>sangdam</v>
+      </c>
+      <c r="C46" t="str">
+        <v/>
+      </c>
+      <c r="D46" t="str">
+        <v>집단 프로그램</v>
+      </c>
+      <c r="E46" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F46" t="str">
+        <v>집단상담</v>
+      </c>
+      <c r="G46" t="str">
+        <v>집단상담_4.jpg</v>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>O</v>
+      </c>
+      <c r="B47" t="str">
+        <v>sangdam</v>
+      </c>
+      <c r="C47" t="str">
+        <v/>
+      </c>
+      <c r="D47" t="str">
+        <v>집단 프로그램</v>
+      </c>
+      <c r="E47" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F47" t="str">
+        <v>집단상담</v>
+      </c>
+      <c r="G47" t="str">
         <v>집단상담.jpg</v>
       </c>
-      <c r="H43" t="str">
-        <v/>
-      </c>
-      <c r="I43" t="str">
-        <v/>
-      </c>
-      <c r="J43" t="str">
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J43"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J47"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/saeop/상담사업.xlsx
+++ b/data/saeop/상담사업.xlsx
@@ -560,7 +560,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J48"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -1017,10 +1017,10 @@
         <v>사진</v>
       </c>
       <c r="F17" t="str">
-        <v>신입회원교육</v>
+        <v>고충처리</v>
       </c>
       <c r="G17" t="str">
-        <v>신입회원교육_(2).jpg</v>
+        <v>고충처리.png</v>
       </c>
       <c r="H17" t="str">
         <v/>
@@ -1052,7 +1052,7 @@
         <v>신입회원교육</v>
       </c>
       <c r="G18" t="str">
-        <v>신입회원교육_(3).jpg</v>
+        <v>신입회원교육_(2).jpg</v>
       </c>
       <c r="H18" t="str">
         <v/>
@@ -1075,16 +1075,16 @@
         <v/>
       </c>
       <c r="D19" t="str">
-        <v>전문상담</v>
+        <v>일반상담</v>
       </c>
       <c r="E19" t="str">
-        <v>설명</v>
+        <v>사진</v>
       </c>
       <c r="F19" t="str">
-        <v/>
+        <v>신입회원교육</v>
       </c>
       <c r="G19" t="str">
-        <v>복지관 이용 회원의 다양한 고민과 어려움 해결을 위한 전문가 상담을 연계하여, 적절한 정보를 제공함으로써 행복한 삶을 살아갈 수 있도록 지원합니다.</v>
+        <v>신입회원교육_(3).jpg</v>
       </c>
       <c r="H19" t="str">
         <v/>
@@ -1110,16 +1110,16 @@
         <v>전문상담</v>
       </c>
       <c r="E20" t="str">
-        <v>정보</v>
+        <v>설명</v>
       </c>
       <c r="F20" t="str">
-        <v>이용 대상</v>
+        <v/>
       </c>
       <c r="G20" t="str">
-        <v>복지관 이용 회원</v>
+        <v>복지관 이용 회원의 다양한 고민과 어려움 해결을 위한 전문가 상담을 연계하여, 적절한 정보를 제공함으로써 행복한 삶을 살아갈 수 있도록 지원합니다.</v>
       </c>
       <c r="H20" t="str">
-        <v>user</v>
+        <v/>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1145,13 +1145,13 @@
         <v>정보</v>
       </c>
       <c r="F21" t="str">
-        <v>이용 시간</v>
+        <v>이용 대상</v>
       </c>
       <c r="G21" t="str">
-        <v>전문 상담 진행 시 개별 안내</v>
+        <v>복지관 이용 회원</v>
       </c>
       <c r="H21" t="str">
-        <v>clock</v>
+        <v>user</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -1177,16 +1177,16 @@
         <v>정보</v>
       </c>
       <c r="F22" t="str">
-        <v>문의</v>
+        <v>이용 시간</v>
       </c>
       <c r="G22" t="str">
-        <v>문화사업팀 033-747-0516</v>
+        <v>전문 상담 진행 시 개별 안내</v>
       </c>
       <c r="H22" t="str">
-        <v>phone</v>
+        <v>clock</v>
       </c>
       <c r="I22" t="str">
-        <v>033-747-0516</v>
+        <v/>
       </c>
       <c r="J22" t="str">
         <v/>
@@ -1206,19 +1206,19 @@
         <v>전문상담</v>
       </c>
       <c r="E23" t="str">
-        <v>절차제목</v>
+        <v>정보</v>
       </c>
       <c r="F23" t="str">
-        <v/>
+        <v>문의</v>
       </c>
       <c r="G23" t="str">
-        <v>이용 절차</v>
+        <v>문화사업팀 033-747-0516</v>
       </c>
       <c r="H23" t="str">
-        <v/>
+        <v>phone</v>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>033-747-0516</v>
       </c>
       <c r="J23" t="str">
         <v/>
@@ -1238,13 +1238,13 @@
         <v>전문상담</v>
       </c>
       <c r="E24" t="str">
-        <v>절차</v>
+        <v>절차제목</v>
       </c>
       <c r="F24" t="str">
-        <v>사전 접수·상담</v>
+        <v/>
       </c>
       <c r="G24" t="str">
-        <v>신청 기간 안에 사전 접수와 상담을 진행합니다.</v>
+        <v>이용 절차</v>
       </c>
       <c r="H24" t="str">
         <v/>
@@ -1273,10 +1273,10 @@
         <v>절차</v>
       </c>
       <c r="F25" t="str">
-        <v>전문가 상담 일정 안내</v>
+        <v>사전 접수·상담</v>
       </c>
       <c r="G25" t="str">
-        <v>상담 일정을 개별적으로 안내해 드립니다.</v>
+        <v>신청 기간 안에 사전 접수와 상담을 진행합니다.</v>
       </c>
       <c r="H25" t="str">
         <v/>
@@ -1305,10 +1305,10 @@
         <v>절차</v>
       </c>
       <c r="F26" t="str">
-        <v>전문가 상담 진행</v>
+        <v>전문가 상담 일정 안내</v>
       </c>
       <c r="G26" t="str">
-        <v>전문가와 상담을 진행합니다.</v>
+        <v>상담 일정을 개별적으로 안내해 드립니다.</v>
       </c>
       <c r="H26" t="str">
         <v/>
@@ -1334,13 +1334,13 @@
         <v>전문상담</v>
       </c>
       <c r="E27" t="str">
-        <v>내용제목</v>
+        <v>절차</v>
       </c>
       <c r="F27" t="str">
-        <v/>
+        <v>전문가 상담 진행</v>
       </c>
       <c r="G27" t="str">
-        <v>이런 상담을 해드려요</v>
+        <v>전문가와 상담을 진행합니다.</v>
       </c>
       <c r="H27" t="str">
         <v/>
@@ -1366,13 +1366,13 @@
         <v>전문상담</v>
       </c>
       <c r="E28" t="str">
-        <v>내용</v>
+        <v>내용제목</v>
       </c>
       <c r="F28" t="str">
-        <v>스트레스 상담</v>
+        <v/>
       </c>
       <c r="G28" t="str">
-        <v>우울 및 스트레스 등 정신건강 관련 상담</v>
+        <v>이런 상담을 해드려요</v>
       </c>
       <c r="H28" t="str">
         <v/>
@@ -1401,10 +1401,10 @@
         <v>내용</v>
       </c>
       <c r="F29" t="str">
-        <v>전문 심리상담</v>
+        <v>스트레스 상담</v>
       </c>
       <c r="G29" t="str">
-        <v>개인 심리상담</v>
+        <v>우울 및 스트레스 등 정신건강 관련 상담</v>
       </c>
       <c r="H29" t="str">
         <v/>
@@ -1436,7 +1436,7 @@
         <v>전문 심리상담</v>
       </c>
       <c r="G30" t="str">
-        <v>부부 갈등 완화를 위한 상담 등</v>
+        <v>개인 심리상담</v>
       </c>
       <c r="H30" t="str">
         <v/>
@@ -1462,13 +1462,13 @@
         <v>전문상담</v>
       </c>
       <c r="E31" t="str">
-        <v>사진</v>
+        <v>내용</v>
       </c>
       <c r="F31" t="str">
-        <v>전문상담</v>
+        <v>전문 심리상담</v>
       </c>
       <c r="G31" t="str">
-        <v>일반상담.jpg</v>
+        <v>부부 갈등 완화를 위한 상담 등</v>
       </c>
       <c r="H31" t="str">
         <v/>
@@ -1500,7 +1500,7 @@
         <v>전문상담</v>
       </c>
       <c r="G32" t="str">
-        <v>전문상담_(2).jpg</v>
+        <v>일반상담.jpg</v>
       </c>
       <c r="H32" t="str">
         <v/>
@@ -1532,7 +1532,7 @@
         <v>전문상담</v>
       </c>
       <c r="G33" t="str">
-        <v>전문상담_(3).jpg</v>
+        <v>전문상담_(2).jpg</v>
       </c>
       <c r="H33" t="str">
         <v/>
@@ -1564,7 +1564,7 @@
         <v>전문상담</v>
       </c>
       <c r="G34" t="str">
-        <v>전문상담_(4).jpg</v>
+        <v>전문상담_(3).jpg</v>
       </c>
       <c r="H34" t="str">
         <v/>
@@ -1587,16 +1587,16 @@
         <v/>
       </c>
       <c r="D35" t="str">
-        <v>집단 프로그램</v>
+        <v>전문상담</v>
       </c>
       <c r="E35" t="str">
-        <v>부제</v>
+        <v>사진</v>
       </c>
       <c r="F35" t="str">
-        <v/>
+        <v>전문상담</v>
       </c>
       <c r="G35" t="str">
-        <v>노년기 우울예방 프로그램</v>
+        <v>전문상담_(4).jpg</v>
       </c>
       <c r="H35" t="str">
         <v/>
@@ -1622,13 +1622,13 @@
         <v>집단 프로그램</v>
       </c>
       <c r="E36" t="str">
-        <v>설명</v>
+        <v>부제</v>
       </c>
       <c r="F36" t="str">
         <v/>
       </c>
       <c r="G36" t="str">
-        <v>비슷한 어려움을 가진 어르신들이 함께 참여하는 집단 활동으로, 우울을 예방하고 서로 어울리며 건강한 노년을 보내실 수 있도록 지원합니다.</v>
+        <v>노년기 우울예방 프로그램</v>
       </c>
       <c r="H36" t="str">
         <v/>
@@ -1654,16 +1654,16 @@
         <v>집단 프로그램</v>
       </c>
       <c r="E37" t="str">
-        <v>정보</v>
+        <v>설명</v>
       </c>
       <c r="F37" t="str">
-        <v>이용 대상</v>
+        <v/>
       </c>
       <c r="G37" t="str">
-        <v>우울 예방 프로그램 참여를 희망하는 복지관 이용 회원</v>
+        <v>비슷한 어려움을 가진 어르신들이 함께 참여하는 집단 활동으로, 우울을 예방하고 서로 어울리며 건강한 노년을 보내실 수 있도록 지원합니다.</v>
       </c>
       <c r="H37" t="str">
-        <v>user</v>
+        <v/>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -1689,13 +1689,13 @@
         <v>정보</v>
       </c>
       <c r="F38" t="str">
-        <v>운영 시간</v>
+        <v>이용 대상</v>
       </c>
       <c r="G38" t="str">
-        <v>7월 · 매주 목요일 10:00 – 11:30</v>
+        <v>우울 예방 프로그램 참여를 희망하는 복지관 이용 회원</v>
       </c>
       <c r="H38" t="str">
-        <v>clock</v>
+        <v>user</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -1721,13 +1721,13 @@
         <v>정보</v>
       </c>
       <c r="F39" t="str">
-        <v>신청 방법</v>
+        <v>운영 시간</v>
       </c>
       <c r="G39" t="str">
-        <v>신청 기간 내 사전 신청</v>
+        <v>7월 · 매주 목요일 10:00 – 11:30</v>
       </c>
       <c r="H39" t="str">
-        <v>edit</v>
+        <v>clock</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -1753,16 +1753,16 @@
         <v>정보</v>
       </c>
       <c r="F40" t="str">
-        <v>문의</v>
+        <v>신청 방법</v>
       </c>
       <c r="G40" t="str">
-        <v>문화사업팀 033-747-0516</v>
+        <v>신청 기간 내 사전 신청</v>
       </c>
       <c r="H40" t="str">
-        <v>phone</v>
+        <v>edit</v>
       </c>
       <c r="I40" t="str">
-        <v>033-747-0516</v>
+        <v/>
       </c>
       <c r="J40" t="str">
         <v/>
@@ -1782,19 +1782,19 @@
         <v>집단 프로그램</v>
       </c>
       <c r="E41" t="str">
-        <v>내용제목</v>
+        <v>정보</v>
       </c>
       <c r="F41" t="str">
-        <v/>
+        <v>문의</v>
       </c>
       <c r="G41" t="str">
-        <v>이런 활동을 해요</v>
+        <v>문화사업팀 033-747-0516</v>
       </c>
       <c r="H41" t="str">
-        <v/>
+        <v>phone</v>
       </c>
       <c r="I41" t="str">
-        <v/>
+        <v>033-747-0516</v>
       </c>
       <c r="J41" t="str">
         <v/>
@@ -1814,13 +1814,13 @@
         <v>집단 프로그램</v>
       </c>
       <c r="E42" t="str">
-        <v>내용</v>
+        <v>내용제목</v>
       </c>
       <c r="F42" t="str">
-        <v>우울 예방 교육</v>
+        <v/>
       </c>
       <c r="G42" t="str">
-        <v>노년기 우울 예방을 위한 교육</v>
+        <v>이런 활동을 해요</v>
       </c>
       <c r="H42" t="str">
         <v/>
@@ -1849,10 +1849,10 @@
         <v>내용</v>
       </c>
       <c r="F43" t="str">
-        <v>만들기 활동</v>
+        <v>우울 예방 교육</v>
       </c>
       <c r="G43" t="str">
-        <v>캘리그라피 무드등, 키링 등 손으로 만드는 활동</v>
+        <v>노년기 우울 예방을 위한 교육</v>
       </c>
       <c r="H43" t="str">
         <v/>
@@ -1878,13 +1878,13 @@
         <v>집단 프로그램</v>
       </c>
       <c r="E44" t="str">
-        <v>사진</v>
+        <v>내용</v>
       </c>
       <c r="F44" t="str">
-        <v>집단상담</v>
+        <v>만들기 활동</v>
       </c>
       <c r="G44" t="str">
-        <v>집단_상담_3.jpg</v>
+        <v>캘리그라피 무드등, 키링 등 손으로 만드는 활동</v>
       </c>
       <c r="H44" t="str">
         <v/>
@@ -1916,7 +1916,7 @@
         <v>집단상담</v>
       </c>
       <c r="G45" t="str">
-        <v>집단상담_1.jpg</v>
+        <v>집단_상담_3.jpg</v>
       </c>
       <c r="H45" t="str">
         <v/>
@@ -1948,7 +1948,7 @@
         <v>집단상담</v>
       </c>
       <c r="G46" t="str">
-        <v>집단상담_4.jpg</v>
+        <v>집단상담_1.jpg</v>
       </c>
       <c r="H46" t="str">
         <v/>
@@ -1980,21 +1980,53 @@
         <v>집단상담</v>
       </c>
       <c r="G47" t="str">
+        <v>집단상담_4.jpg</v>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>O</v>
+      </c>
+      <c r="B48" t="str">
+        <v>sangdam</v>
+      </c>
+      <c r="C48" t="str">
+        <v/>
+      </c>
+      <c r="D48" t="str">
+        <v>집단 프로그램</v>
+      </c>
+      <c r="E48" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F48" t="str">
+        <v>집단상담</v>
+      </c>
+      <c r="G48" t="str">
         <v>집단상담.jpg</v>
       </c>
-      <c r="H47" t="str">
-        <v/>
-      </c>
-      <c r="I47" t="str">
-        <v/>
-      </c>
-      <c r="J47" t="str">
+      <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J47"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J48"/>
   </ignoredErrors>
 </worksheet>
 </file>